--- a/MASTORION/BIBLIOTHEQUES/BIBLIOTHEQUE_TEST_3_EXERCICES.xlsx
+++ b/MASTORION/BIBLIOTHEQUES/BIBLIOTHEQUE_TEST_3_EXERCICES.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V118"/>
+  <dimension ref="A1:V213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2081,11 +2081,7 @@
           <t>féminin</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>ANIMATION EXERCICE</t>
@@ -2165,11 +2161,7 @@
           <t>masculin</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>ANIMATION EXERCICE</t>
@@ -10489,6 +10481,5378 @@
       </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>arn_weber</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Henri Weber</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>arnweber@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Parcours : Pharmacien de profession, Weber est maire de HSarrebourg depuis 2008. Élu sur une liste supposée apolitique, il est en réalité proche des milieux pro-Mercure du fait de ses origines familiales. Homme de la gestion quotidienne, il n'a aucune expérience des crises majeures. La population de HSarrebourg compte environ 35 % de résidents d'origine mercurienne, ce qui crée des tensions avec les Arnlandais depuis quelques années. | Objectifs : Protéger la diaspora mercurienne de HSarrebourg. Gérer les flux de déplacés du nord-est sans déstabiliser les services municipaux Maintenir le dialogue avec les autorités politiques et militaires des deux camps pour éviter les incidents | Forces : Ancrage local fort Relation de travail établie avec les unités militaires stationnées à proximité Soutien de la diaspora mercurienne | Faiblesses : Dépassé par l'ampleur de la crise humanitaire Ressources municipales insuffisantes face aux besoins Relation tendue avec certaines autorités nationales Attaqué sur le plan personnel par les patriotes arnlandais les plus virulents | Réseaux sociaux : publications régulières sur la vie de la ville. Relai de certains messages pro-Mercure.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Maire (en réserve — sans ville attribuée)</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>arn_hartmann</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Grigori Hartmann</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>arnhartmann@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Parcours : Notaire à la retraite, figure patriarcale d'une ville marquée par la double culture et une proportion de résidents d'origine mercurienne approchant les 50%. Hartmann est maire depuis 2004, réélu sans discontinuer sur des listes pro-MER locales. Mercurianophone, il a longtemps joué la carte identitaire. Sa posture s’est radicalisée depuis l’invasion, se faisant l’un des principaux relais du narratif sur la persécution des Mercuriens en Arnland. | Objectifs : Maintenir sa commune en dehors des violences intercommunautaires directes Préserver son autorité sur le conseil municipal Négocier la protection de ses administrés mercuriens | Forces : Légitimité locale exceptionnelle après vingt ans de mandat Réseau notarial et juridique utilisable pour des négociations Position géographique stratégique de HSarre-Union | Faiblesses : Conseil municipal partiellement pro-ARN Archives notariales contenant des actes sur la situation communautaire, sensibles dans le contexte actuel Attaques sur les réseaux sociaux venant de patriotes ARN Hostilité de certains proches de Radulov du fait de son positionnement | Réseaux sociaux : Présence rare et prudente. Quelques relais de discours pro-MER.</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Maire (en réserve — sans ville attribuée)</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>arn_kovalev</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Dmitri Kovalev</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>arnkovalev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Parcours : Né à HAlberstroff d'une famille mercurienne installée depuis trois générations, Kovalev est petit entrepreneur dans le secteur des matériaux de construction. Élu maire en 2020 d’une ville composée à 40% de diaspora mercurienne, il fait partie des maires ouvertement issus de cette communauté en HLorraine. Sa légitimité repose sur une proximité sociale totale avec ses administrés. Son positionnement pro-Mercure s'est radicalisé depuis l'invasion : il a basculé progressivement sous l'effet conjugué de la pression communautaire locale, de la rhétorique de Volkonsky qu'il fréquente, et de la méfiance croissante qu'il ressent vis-à-vis de l'État arnlandais. | Objectifs : Protéger physiquement ses administrés dans une commune exposée géographiquement Faciliter et promouvoir la présence mercurienne dans la zone Obtenir des garanties pour la communauté mercurienne locale dans le cadre d'un éventuel accord territorial | Forces : Enracinement communautaire total Connaissance intime du terrain rural frontalier et des réseaux informels locaux Capacité à maintenir une façade de légalité républicaine tout en facilitant des actions para-légales | Faiblesses : Dépendance économique personnelle : son entreprise tourne au ralenti Jeunesse et inexpérience politique : manipulable par des acteurs plus aguerris des deux camps Famille élargie partiellement en zone arnlandaise : vulnérabilité émotionnelle exploitable pour le ramener vers une posture plus modérée | Réseaux sociaux : publica...</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Maire De Halberstroff</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>arn_nathalie_martin</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Nathalie Martin</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>arnnathaliemartin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Parcours : Ancienne responsable RH dans une PME industrielle de la région, Martin a été élue maire de HSarre-Union en 2020. Elle a hérité d'une ville à forte proportion mercurienne (~35 %) et d'une posture politique d'équilibre qu'elle cherche à maintenir publiquement même si celle-ci est artificielle. Amie personnelle de Serge Mordidchev (HNancy) et de Robert Danevois (HChateau-Salins), elle s'inscrit dans un réseau d'élus lorrains liés au réseau pro-MER. Sa position se complique du fait de sa fille, Kimberley Martin, dont les liens avec deux militaires arnlandais suspectés de sympathies pro-Mercure — Thomas Crusadier et Pascal Degardin — ainsi qu'avec un individu anonyme pro-Mercure, font l'objet d'une attention croissante des services de Radulov. | Objectifs : Maintenir HSarre-Union en dehors des violences intercommunautaires directes Préserver son autorité sur un conseil municipal hérité, qu'elle ne contrôle pas totalement Protéger sa fille des conséquences judiciaires potentielles de ses fréquentations | Forces : Légitimité locale construite dans la continuité d'un mandat stable Réseau amical avec Mordidchev et Danevois lui donnant un accès informel aux dynamiques politiques lorraines Profil bas qui la maintient sous le radar des acteurs nationaux, lui laissant une marge de manœuvre locale Connaissance des dynamiques sociales utile pour gérer les tensions intercommunautaires au quotidien | Faiblesses : Situation de Kimberley : levier de pression considérable, utilisable...</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26;RESEAU RZO</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Maire de HSarre-Union (2 700 hab., HLorraine orientale)</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>arn_robert_danevois</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Robert Danevois</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>arnrobertdanevois@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Parcours : Jeune entrepreneur dans le secteur de la rénovation du bâtiment, Danevois a été élu maire de HChateau-Salins en 2020, surprenant les observateurs locaux par sa victoire face à un sortant bien installé. Son élection reposait sur un programme de revitalisation économique d'une commune en lent déclin. Ami personnel de Serge Mordidchev (HNancy) et de Nadia Promesy (HSarrebourg), il s'inscrit dans le même réseau informel d'élus lorrains entretenant des liens avec la communauté mercurienne. Sa connexion la plus problématique est son lien suspecté — non confirmé — avec Léon-Philippe Thely, agitateur pro-Mercure actif dans la zone, dont il aurait été proche dans sa jeunesse et avec lequel des contacts discrets auraient été maintenus. Danevois reste cependant discret en public quant à son positionnement sur le conflit. | Objectifs : Préserver l'économie locale de l'effondrement lié à la crise Maintenir sa commune viable face à la dépopulation accélérée par la guerre Gérer discrètement ses relations compromettantes sans s'exposer | Forces : Capacité entrepreneuriale : capacité à identifier des solutions économiques créatives en situation de crise Réseau amical avec Mordidchev, donnant accès indirect aux ressources et à la visibilité de HNancy Profil d'élu rural peu scruté par les médias nationaux, ce qui lui laisse une latitude d'action locale | Faiblesses : Lien suspecté avec Thely : si documenté, compromettant pour lui-même et par ricochet pour Mordidchev et Promesy Inexpé...</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26;RESEAU RZO</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>Maire de HChateau-Salins (2 300 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>arn_kovacic</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Luka Kovacic</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>arnkovacic@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Parcours : Issu d'une famille d'immigrés mercuriens installés dans le Grand Est, Luka Kovacic accorde une grande importance à ses origines familiales et à la religion protestante, devenant un fidèle de Piotr Volkonsky. C'est son deuxième mandat à la mairie de HMirecourt. Même si cette commune de 4 700 habitants n'est composée qu'à 15 % de Mercuriens d'origine, il bénéficie de leur forte capacité de mobilisation électorale au sein d'une population relativement apathique politiquement. | Objectifs : Protéger la communauté mercurienne de HMirecourt. Éviter d'être débordé par l'afflux de réfugiés. | Forces : Fort soutien de la communauté mercurienne de HMirecourt. Stabilité en tant que maire. Légitimité acquise par sa politique de valorisation du patrimoine local. | Faiblesses : Flux de réfugiés vers l'Ouest qui se poursuivent depuis le début du conflit. Petite commune qui manque de moyens. Hostilité des nationalistes arnlandais. | Réseaux sociaux : Communication discrète.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>Maire de HMirecourt (4 700 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>bot_viklund</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Oskar Viklund</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>botviklund@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Parcours : Oskar Viklund est issu d'une famille mêlant racines bothniennes et mercuriennes. Théologien conservateur, il s'est fait connaître pour ses travaux sur l'héritage culturel commun de l'ancien Empire Skolkan. Durant les années 2000, il devient une figure importante de l'Église Réformée de Bothnie, minoritaire mais influente dans certaines régions de l'est du pays. Il développe un discours favorable à une coopération étroite entre les peuples héritiers de l'espace skolkan et critique régulièrement ce qu'il considère comme l'expansion des institutions occidentales dans la région. Défendre les traditions chrétiennes historiques. Renforcer les liens culturels avec les peuples voisins. Préserver l'héritage skolkan. Limiter l'influence culturelle occidentale. Favoriser le dialogue entre communautés bothniennes et mercuriennes. Forte influence dans l'est du pays. Réseau ecclésiastique transfrontal</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>BOT - RELIGIEUX;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>RELIGIEUX</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>Église Réformée — PRO-MER</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>rzo_louis_yarbot</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Louis YARBOT</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>rzo_louis_yarbot@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>Adjoint</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>rzo_bernard_lecone</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bernard LECONE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>rzo_bernard_lecone@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>Geek-Cyber</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>rzo_eric_hervouet</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Éric HERVOUET</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>rzo_eric_hervouet@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Artificier</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>rzo_marie_nassah</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Marie NASSAH</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>rzo_marie_nassah@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ARN - PRO-MERCURE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>PRO-MERCURE</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Influenceuse Pro-MER</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr"/>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>rzo_bea_hvt</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Béa_HVT</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>rzo_bea_hvt@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ARN - PRO-MERCURE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>PRO-MERCURE</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Complotiste Pro-MER</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr"/>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>rzo_cathy_pommerond</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Cathy POMMEROND</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>rzo_cathy_pommerond@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ARN - PRO-MERCURE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>PRO-MERCURE</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>Commerçante Pro-MER</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr"/>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>rzo_firmin_lapotre</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Firmin LAPOTRE</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>rzo_firmin_lapotre@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>Instructeur Guérilla</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr"/>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>rzo_gennady_yeremin</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Gennady YEREMIN</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>rzo_gennady_yeremin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>42 e DIV</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>rzo_katia_chapman</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Katia CHAPMAN</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>rzo_katia_chapman@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>MER - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Célébrité MER</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>rzo_armin_krasni</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Armin KRASNI</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>rzo_armin_krasni@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>43 e DIV</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr"/>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>rzo_x_3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Капитан Хэдок</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>rzo_x_3@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ARN - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Influenceur</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr"/>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>rzo_the_flying_fly</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>The flying fly</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>rzo_the_flying_fly@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ARN - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>Agitateur</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr"/>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>rzo_le_padupe</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Le Padupe</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>rzo_le_padupe@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>ARN - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>Agitateur</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr"/>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_1</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Anonymous #1</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_1@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>Compte anonyme (agitation)</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr"/>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_2</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Anonymous #2</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_2@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>Compte anonyme</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr"/>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_3</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Anonymous #3</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_3@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>Compte anonyme</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr"/>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_4</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Anonymous #4</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_4@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>Compte anonyme</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr"/>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_5</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Anonymous #5</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>rzo_anonymous_5@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>Compte anonyme</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr"/>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>rzo_abramovitch_milanov</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Abramovitch MILANOV</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>rzo_abramovitch_milanov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>Arkan</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr"/>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>rzo_aslan_maskhadan</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Aslan MASKHADAN</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>rzo_aslan_maskhadan@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>BAT 1 XO</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>rzo_ismail_yamadayev</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ismail YAMADAYEV</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>rzo_ismail_yamadayev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>rzo_magomed_aslanbekov</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Magomed ASLANBEKOV</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>rzo_magomed_aslanbekov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>rzo_mayrbek_zelimkhanov</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mayrbek ZELIMKHANOV</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>rzo_mayrbek_zelimkhanov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>HQ Coy</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>rzo_lziov_murner</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lziov MURNER</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>rzo_lziov_murner@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>HQ Coy</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>rzo_mahmut_zoun</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Mahmut ZOUN</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>rzo_mahmut_zoun@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>rzo_mirnek_azoff</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Mirnek AZOFF</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>rzo_mirnek_azoff@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>rzo_niek_snurt</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Niek SNURT</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>rzo_niek_snurt@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>2Coy</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>rzo_zardar_petrov</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Zardar PETROV</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>rzo_zardar_petrov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>rzo_vassiliev_zdar</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Vassiliev ZDAR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>rzo_vassiliev_zdar@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>rzo_ilyas_shishani</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ilyas SHISHANI</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>rzo_ilyas_shishani@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>rzo_vassiliev_anzor</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Vassiliev ANZOR</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>rzo_vassiliev_anzor@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>rzo_akbolat_vakha</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Akbolat VAKHA</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>rzo_akbolat_vakha@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Lieutenant</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>rzo_tamerlan_dzhabrailov</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Tamerlan DZHABRAILOV</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>rzo_tamerlan_dzhabrailov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>rzo_said_chechensky</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Said CHECHENSKY</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>rzo_said_chechensky@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>rzo_eleny_svirkof</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Eleny SVIRKOF</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>rzo_eleny_svirkof@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>rzo_niko_trakk</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Niko TRAKK</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>rzo_niko_trakk@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>rzo_mindun_flak</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Mindun FLAK</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>rzo_mindun_flak@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>rzo_kurt_zweiter</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Kurt ZWEITER</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>rzo_kurt_zweiter@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>rzo_zulun_pretor</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Zulun PRETOR</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>rzo_zulun_pretor@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>2Coy</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>rzo_shamil_abubakarov</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Shamil ABUBAKAROV</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>rzo_shamil_abubakarov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>BAT 1 XO</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr"/>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>rzo_timur_elmurzaev</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Timur ELMURZAEV</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>rzo_timur_elmurzaev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr"/>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>rzo_zaur_idrisov</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Zaur IDRISOV</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>rzo_zaur_idrisov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr"/>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>rzo_zelimkhan_muradov</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Zelimkhan MURADOV</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>rzo_zelimkhan_muradov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>HQ Coy</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr"/>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>rzo_alkhazour_lors</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Alkhazour LORS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>rzo_alkhazour_lors@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>Lieutenant</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr"/>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>rzo_mikhail_volkov</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Mikhail VOLKOV</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>rzo_mikhail_volkov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr"/>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>rzo_pavel_smirnov</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Pavel SMIRNOV</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>rzo_pavel_smirnov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>rzo_egor_fiodorov</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Egor FIODOROV</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>rzo_egor_fiodorov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr"/>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>rzo_georgui_sokolov</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Georgui SOKOLOV</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>rzo_georgui_sokolov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>2Coy</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr"/>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>rzo_dmitri_ivanov</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Dmitri IVANOV</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>rzo_dmitri_ivanov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>rzo_viktor_aldam</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Viktor ALDAM</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>rzo_viktor_aldam@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Lieutenant</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>rzo_igor_tarasovitch</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Igor TARASOVITCH</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>rzo_igor_tarasovitch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>3Coy</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>rzo_youri_larionovitch</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Youri LARIONOVITCH</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>rzo_youri_larionovitch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>4Coy</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>rzo_matvei_filipovitch</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Matvei FILIPOVITCH</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>rzo_matvei_filipovitch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>2Coy</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>rzo_piotr_leonidovitch</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Piotr LEONIDOVITCH</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>rzo_piotr_leonidovitch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>UAV Coy</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>rzo_serguei_mamaiev</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Serguei MAMAIEV</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>rzo_serguei_mamaiev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>HQ Coy</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>rzo_artiom_obnizov</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Artiom OBNIZOV</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>rzo_artiom_obnizov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>1Coy</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>rzo_edil_kalo</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Edil KALO</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>rzo_edil_kalo@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>Lieutenant</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>rzo_viktor_g_kaleva</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Viktor G KALEVA</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>rzo_viktor_g_kaleva@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>HYBRID FORCES</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>rzo_carl_slagbygle</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Carl SLAGBYGLE</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>rzo_carl_slagbygle@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>SKOLKAN OPS CELL</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>rzo_oskar_sandell</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Oskar SANDELL</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>rzo_oskar_sandell@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>OVERSEAS OPS CELL</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>rzo_sture_malmgren</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Sture MALMGREN</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>rzo_sture_malmgren@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>INFO OPS CELL</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>rzo_freddy_flinsten</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Freddy FLINSTEN</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>rzo_freddy_flinsten@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>2IC NOM</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>rzo_wilma_smasten</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Wilma SMASTEN</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>rzo_wilma_smasten@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>Leader NOM</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>rzo_betty_spilror</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Betty SPILROR</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>rzo_betty_spilror@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>CI &amp; INTEL CELL</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>rzo_the_cat</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>« The CAT »</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>rzo_the_cat@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>Team leader #30 — cellule HParis</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>rzo_vito</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>« Vito »</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>rzo_vito@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>LOG support — cellule HParis</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>rzo_voyou</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>« Voyou »</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>rzo_voyou@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>Team leader #30 — cellule HLille</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>rzo_emeritus</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>« Emeritus »</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>rzo_emeritus@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>Leader — cellule HMarseille</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>rzo_prophet</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>« Prophet »</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>rzo_prophet@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>Recruteur — cellule HMarseille</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>rzo_the_trello</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>« The Trello »</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>rzo_the_trello@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>Team leader #30 — cellule HMarseille</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>rzo_agent_11</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Agent #11</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>rzo_agent_11@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HParis</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>rzo_agent_12</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Agent #12</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>rzo_agent_12@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HParis</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>rzo_agent_21</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Agent #21</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>rzo_agent_21@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HLille</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>rzo_agent_22</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Agent #22</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>rzo_agent_22@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HLille</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>rzo_agent_31</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Agent #31</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>rzo_agent_31@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HMarseille</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>rzo_agent_32</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Agent #32</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>rzo_agent_32@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>Agent anonyme — cellule HMarseille</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>rzo_arkadi_andronikov</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Arkadi ANDRONIKOV</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>rzo_arkadi_andronikov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>Assistant Director</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>rzo_denis_antonov</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Denis ANTONOV</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>rzo_denis_antonov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>Photographer</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>rzo_vassili_glebov</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Vassili GLEBOV</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>rzo_vassili_glebov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Safety Officer</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>rzo_lioubov_bourkov</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Lioubov BOURKOV</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>rzo_lioubov_bourkov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>Head Activity Officer</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>rzo_boris_vostrikov</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Boris VOSTRIKOV</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>rzo_boris_vostrikov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>Activity Officer</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>rzo_vadim_jdanov</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Vadim JDANOV</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>rzo_vadim_jdanov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>Dealer Sponsor</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>rzo_oskar_cascarich</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Oskar CASCARICH</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>rzo_oskar_cascarich@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>Aire Vignes Sud manager</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>rzo_ravisk_olevitch</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Ravisk OLEVITCH</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>rzo_ravisk_olevitch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>HFM LOG officer</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>rzo_pavel_vodianov</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Pavel VODIANOV</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>rzo_pavel_vodianov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>Young Officer</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>rzo_oleg_raskine</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Oleg RASKINE</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>rzo_oleg_raskine@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>Honorary member</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>rzo_ievgueni_gretchko</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Ievgueni GRETCHKO</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>rzo_ievgueni_gretchko@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>Treasurer &amp; Membership</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>rzo_aleksei_ibraguimov</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Alekseï IBRAGUIMOV</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>rzo_aleksei_ibraguimov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ARN - GROUPE CLANDESTIN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10501,7 +15865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V72"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16396,6 +21760,1130 @@
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>arn_pallesson</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sture Pallesson</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>arnpallesson@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Parcours : Fils d'un industriel du secteur minier, Pallesson a fait ses armes en droit des affaires avant de rejoindre la politique locale dans les années 1990. Élu gouverneur de la région HHauts-de-France au début des années 2000, il construit sa réputation sur un discours réformiste et anti-corruption. Élu Président en 2006 avec un programme ambitieux de moralisation de la vie publique, il fait voter une série de lois anti-corruption saluées par la presse internationale — mais qui restent lettre morte dans leur application. Battu en 2014 dans un contexte de désillusion générale, il passe dix ans dans le secteur privé (conseil en stratégie, think tanks libéraux-conservateurs). Sa réélection récente est analysée la crise sécuritaire : son image d'homme d'État expérimenté, combinée à la faiblesse de ses adversaires, l'emporte sur le souvenir de ses échecs. | Objectifs : Maintenir l'intégrité territoriale d'Arnland face à l'invasion mercurienne Obtenir un soutien diplomatique et militaire international Restaurer son image de réformateur crédible en temps de crise | Forces : Expérience gouvernementale Capacité rhétorique et image présidentielle rassurante Légitimité électorale récente dans un contexte de crise | Faiblesses : Incapacité à régler les problèmes de corruption en Arnland Tendance à privilégier la communication sur l'action Fragilité de sa coalition au Parlement en temps de guerre Accusé de discrimination à l’encontre de la diaspora mercurienne Vu comme une personnali...</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>President De La Republique</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>arn_karrlson</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Vincent Karrlson</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>arnkarrlson@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Parcours : Issu d'une famille de la moyenne bourgeoisie du HCentre-Val-de-Loire, Karrlson est un apparatchik de l'APP pur produit : sciences politiques, cabinet ministériel dès 28 ans, directeur de cabinet du Trésor sous le premier mandat Pallesson. Élu député à trois reprises dans une circonscription industrielle, il s'est imposé comme un gestionnaire rigoureux, peu charismatique mais efficace dans la négociation parlementaire. Sa nomination comme Premier ministre est avant tout un choix de loyauté et de stabilité : Pallesson sait qu'il ne lui fera pas d'ombre car Karrlson n'a pas de base électorale propre. | Objectifs : Assurer la continuité de l'État et le fonctionnement des services publics en temps de crise Coordonner l'effort de guerre sur le plan administratif et budgétaire Maintenir la cohésion de la majorité parlementaire | Forces : Maîtrise de dossiers techniques Réseau dense au sein des autorités locales pro-Arnland et pro-OTAN Loyauté sans ambiguïté envers Pallesson, ce qui lui confère une marge d'action réelle | Faiblesses : Absence totale de charisme populaire dans un contexte où la mobilisation civile est cruciale Peu de légitimité propre en cas de vacance du pouvoir, forte dépendance vis-à-vis de ses alliés politiques Mal à l'aise dans la gestion des crises médiatiques Fragilité de la coalition au Parlement en temps de guerre | Réseaux sociaux : Présence minimale, uniquement institutionnelle. Publie des communiqués officiels sur X. Pas de stratégie personnelle...</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Premier Ministre</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>arn_jankovic</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Mira Jankovic</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>arnjankovic@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Parcours : Diplômée de l’Université de HParis en relations internationales, elle intègre le corps diplomatique au début des années 1990 puis sert dans plusieurs ambassades européennes, en se spécialisant dans les relations avec l’UE. Occupant la fonction de conseillère diplomatique de la Présidence arnlandaise avant sa nomination comme Ministre des Affaires étrangères, elle est réputée pour ses capacités de communication et de négociation. | Objectifs : Consolider le soutien international Contenir les ingérences étrangères et la guerre informationnelle Préserver la crédibilité diplomatique malgré les scandales de corruption internes | Forces : Excellente connaissance des institutions multilatérales Crédibilité internationale et réseau diplomatique étendu Maîtrise d’une rhétorique puissante contre le narratif mercurien | Faiblesses : Suspicion sourde au sein de l'APP sur ses loyautés réelles Sous pression constante pour prouver sa fermeté vis-à-vis de Mercure Egalement attaquée sur le plan personnel par des réseaux pro-Mercure Dans ce contexte, préoccupée par la possibilité de maintenir des alliances solides avec ses partenaires européens. | Réseaux sociaux : Active sur X. Ligne éditoriale : diplomatie offensive, diffusion de contre-narratifs face à la propagande mercurienne, tribunes et citations de droit international. Ton mesuré mais déterminé. Suivie par des médias étrangers.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Ministre Des Affaires Etrangeres</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>arn_belov</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Andrei Belov</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>arnbelov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Parcours : Ingénieur de formation, Daniel Schmidt est ingénieur de formation, issu du complexe militaro-industriel arnlandais. A partir du début des années 2010, il occupe des postes de direction au sein d’agences d’armement et de logistique de défense avant de rejoindre le ministère. Jouissant de la confiance du Président, sa nomination comme Ministre de la Défense vise à rétablir une forme de consensus dans un contexte de lutte contre la corruption. | Objectifs : Assurer la continuité opérationnelle des forces armées Faire face à la lutte informationnelle Contenir les scandales internes Contenir les luttes d’influence | Forces : Connaissance opérationnelle du terrain et du dispositif militaire Crédibilité auprès des officiers et de l'état-major Communication appréciée dans les cercles militaires | Faiblesses : Dépendance de l’armée arnlandaise vis-à-vis de l’OTAN Tensions avec Karrlson sur les arbitrages budgétaires Critiques de la population pour son incapacité à mener une politique de défense dissuasive vis-à-vis de Mercure. | Réseaux sociaux : Faible activité. Publication de bulletins opérationnels sobres sur le site du ministère. Les journalistes se plaignent d'un accès difficile.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Ministre De La Defense</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>arn_radulov</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Dmitri Radulov</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>arnradulov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Parcours : Après avoir occupé des postes à responsabilité au sein de l’ASPS, Radulov s'est bâti une réputation d'homme dur sur les dossiers de criminalité organisée — avec des méthodes parfois contestées par les instances de contrôle. Proche des réseaux conservateurs de l'APP, il a été propulsé au ministère de l'Intérieur comme contrepoids à l'aile libérale du gouvernement. Son nom a circulé dans plusieurs affaires de surveillance abusive avant son entrée au gouvernement, sans jamais aboutir à des poursuites. Depuis l'invasion, il est en première ligne sur les questions de sécurité intérieure. | Objectifs : Neutraliser les réseaux de soutien à Mercure sur le territoire arnlandais Sécuriser les infrastructures critiques contre le sabotage Maintenir l'ordre public dans un contexte de tensions intercommunautaires croissantes | Forces : Expérience du renseignement intérieur et des opérations contre-subversives Réseau dense dans les forces de l'ordre et la magistrature Déterminé et peu sensible aux pressions politiques de court terme | Faiblesses : Tendance à l'abus de pouvoir et risque de dérive autoritaire Mesures ciblant la diaspora mercurienne susceptibles d'alimenter la radicalisation Friction constante avec Jankovic sur l'image internationale d'Arnland Les critiques à son encontre viennent également d’autres ministres et de députés de son propre camp | Réseaux sociaux : actif, avec une ligne populiste-sécuritaire assumée. Messages courts, fermes, parfois provocateurs à desti...</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Ministre De L’Interieur</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>arn_birkmann</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Augustin Birkmann</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>arnbirkmann@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Parcours : Formé au sein de l’école d’administration arnlandaise, Birkmann a fait toute sa carrière dans le corps préfectoral. Il a été préfet de département en HBretagne et en HHauts-de-France avant d'être nommé à HGrand Est il y a trois ans. L'invasion a transformé ce poste en l'un des plus exposés de la République. Homme de procédures, il est respecté pour son intégrité mais peine à s'adapter au rythme et à la violence de la crise. Il entretient des relations difficiles avec Radulov, dont il conteste régulièrement les injonctions sécuritaires sur le plan légal. | Objectifs : Maintenir la légalité républicaine dans une région partiellement occupée ou contestée Coordonner l'action de l'État entre les maires pro-Arnland et les autorités locales pro-Mercure Gérer les flux de déplacés internes et l'approvisionnement des zones de crise | Forces : Capacité à communiquer avec les deux camps en tant représentant de l'État Solide connaissance du droit administratif en situation exceptionnelle Relation positive avec les représentants de l’OTAN dans la région | Faiblesses : Inadapté au tempo des crises militaires et médiatiques Manque d'autorité politique réelle face aux élus locaux qui jouent leur propre jeu Isolement croissant : ses supérieurs au niveau national ne comprennent pas les réalités du terrain Peu connu de la population malgré ses ambitions politiques | Réseaux sociaux : Aucune présence personnelle. Communiqués officiels au nom de la préfecture.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Prefet De La Region Hlorraine</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>arn_gervais</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Emile Gervais</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>arngervais@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Parcours : Élu en 2020, 44 ans, né dans la commune. Marié, 2 enfants, en instance de divorce. Ingénieur en aménagement du territoire avant son mandat. Études à HNANCY, en poste dans un cabinet spécialisé à Vandœuvre-lès-Nancy pendant 10 ans avant de revenir à HNEUFCHATEAU. | Objectifs : Donner une dynamique à sa ville, revitaliser le centre-ville, attirer de jeunes diplômés. Encourager la transition écologique. | Forces : Pragmatique et à l'écoute, proche des habitants. | Faiblesses : Peu à l'aise avec le compromis, très attaché à son image. Inexpérience des questions militaires et sécuritaires ; délègue très facilement, avec une possible confiance excessive en ses collaborateurs. | Réseaux sociaux : Très actif. Ligne éditoriale : « maire en action ». Publie quotidiennement. Audience locale.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Maire HNEUFCHATEAU</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>arn_thiebaut</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bernard Thiebaut</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>arnthiebaut@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Parcours : Agriculteur céréalier à la retraite, Thiebaut est maire de HChateau-Salins depuis 2001 sans interruption. Figure de la ruralité profonde, il incarne un monde de la politique locale qui n'a que peu de rapports avec les grandes métropoles. Sa commune, proche de la zone de combats, a vu partir une partie de sa population et accueille des soldats arnlandais en cantonnement. Vieux-jeu sur la forme mais fin connaisseur des réseaux locaux, il a des liens familiaux avec des familles mercuriennes de la frontière — ce qui complique sa position depuis l'invasion. | Objectifs : Maintenir sa commune debout dans un contexte de dépopulation accélérée par la guerre Garantir la sécurité physique de ses administrés restants Préserver des liens de bon voisinage avec les familles mercuriennes présentes, sans paraître complaisant | Forces : Connaissance intime du terrain et des réseaux humains locaux Crédibilité personnelle intacte après plus de vingt ans de mandat Capacité à trouver des arrangements pratiques là où l'État bureaucratique échoue | Faiblesses : Isolement institutionnel : commune trop petite pour peser dans les arbitrages régionaux Liens familiaux transfrontaliers susceptibles d'être mal interprétés Difficulté en matière de communication | Réseaux sociaux : Aucune communication</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Maire (en réserve — sans ville attribuée)</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>arn_krauss</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Isabelle Krauss</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>arnkrauss@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Parcours : Professeure des écoles reconvertie en politique locale et patriote arnlandaise, Krauss a été élue en 2014 sur un programme de redynamisation économique d'une ville en déclin industriel. Femme de dossiers, méthodique, elle a obtenu plusieurs financements régionaux pour la rénovation urbaine de HLunéville. Proche de l'aile sociale de l'APP, elle entretient de bons rapports avec Karrlson, dont elle était une soutien lors des primaires internes. | Objectifs : Transformer HLunéville en base arrière efficace pour l'effort de guerre (hôpital de campagne, logistique) Protéger l'économie locale de l'effondrement lié à la crise Se positionner comme relais fidèle et efficace de l'État central dans sa région | Forces : Rigueur administrative et capacité à mobiliser des financements d'urgence Bonne relation avec les autorités militaires présentes sur le territoire Crédibilité auprès de l'électorat populaire arnlandais patriote | Faiblesses : Manque de charisme dans la communication de crise HLunéville manque de moyens hospitaliers Gestion d’une crise qui dépasse ses attributions habituelles Dépendance vis-à-vis d’acteurs extérieurs pour maintenir les financements de la ville | Réseaux sociaux : Présente sur Facebook et ArnNet. Ligne éditoriale : information pratique, solidarité, appels aux bénévoles. Ton institutionnel mais chaleureux.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Maire (en réserve — sans ville attribuée)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>arn_voloshyn</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Irina Voloshyn</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>arnvoloshyn@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Parcours : Ancienne directrice d'un centre de formation professionnelle, Voloshyn a été élue maire de HToul en 2018 en renversant une majorité APP installée depuis vingt ans. Son programme : revitalisation d'une ville en désindustrialisation avancée, reconversion du patrimoine laissé à l'abandon, et développement du tissu associatif. Femme de conviction sociale-démocrate, elle entretient des liens étroits avec le secteur associatif et les syndicats locaux. Son positionnement pro-Arnland est idéologique autant que pragmatique : elle est convaincue que la démocratie arnlandaise, malgré ses défauts, est infiniment préférable à l'autoritarisme mercurien. Ses relations avec la préfecture sont tendues : elle réclame des moyens que Birkmann ne peut pas débloquer seul. | Objectifs : Gérer les flux humanitaires vers HToul Obtenir des financements d'urgence de l'État et des organisations internationales Maintenir la cohésion sociale d'une ville déjà fragilisée économiquement avant la guerre | Forces : Réseau associatif et syndical dense, mobilisable rapidement Légitimité forte auprès des populations défavorisées et des déplacés Capacité de communication pour mobiliser l'opinion publique nationale sur la question humanitaire | Faiblesses : Dépendance aux financements extérieurs Opposition politique au gouvernement Pallesson qui complique les relations avec l'État central en temps de crise Surcharge administrative visible Profil militant connu : Radulov dispose de dossiers sur ses réseau...</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Maire De Htoul</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>arn_nadia_promesy</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Nadia Promesy</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>arnnadiapromesy@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Parcours : Pharmacienne de formation, Promesy a repris la pharmacie familiale avant de se lancer en politique locale à 33 ans, élue sur une liste d'union apolitique. Son positionnement pro-Arnland est sincère mais mesuré : elle croit dans les institutions arnlandaises tout en reconnaissant leurs défaillances. Ses amitiés politiques la situent dans le réseau lorrain informel : proche de Jean-Louis Adriane (HLunéville) et de Robert Danevois (HChateau-Salins), elle est ainsi connectée indirectement au réseau gravitant autour de Mordidchev. Cette connexion est suffisamment distante pour ne pas la compromettre, mais suffisamment réelle pour qu'elle soit sollicitée comme relai dans certaines situations. HSarrebourg compte environ 30 % de résidents d'origine mercurienne. Son jeune âge et son profil non-partisan en font une figure encore difficile à catégoriser pour les acteurs nationaux. Avec l'avancée du conflit, HSarrebourg s'est retrouvée au cœur des combats : les tensions entre les communautés arnlandaise et mercurienne s'exacerbent et une partie de la population cherche à fuir — vers l'Ouest pour les pro-ARN, vers l'Est pour les pro-MER. Sa position pro-ARN, sincère mais fragilisée par ses connexions avec la diaspora, devient de plus en plus difficile à tenir. | Objectifs : Préserver la cohésion sociale d'une ville à démographie mixte sous pression Assurer l'accueil des déplacés du nord-est sans déstabiliser les services municipaux Construire une légitimité politique propre san...</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26;RESEAU RZO</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Maire de HSarrebourg (12 000 hab., Hlorraine)</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>arn_katia_volkov</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Katia Volkov</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>arnkatiavolkov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Parcours : Ancienne cadre dans une entreprise de logistique à HNancy, Katia Volkov est revenue dans son village natal de HVaucouleurs pour y élever ses enfants, avant d'en devenir maire à la faveur d'une élection surprise. Sans étiquette, elle cherche à attirer de nouvelles familles et à développer le télétravail ; son dynamisme séduit les jeunes mais irrite parfois les anciens. Traits : ambitieuse, énergique, diplomate, parfois impatiente. | Objectifs : Revitaliser HVaucouleurs (nouvelles familles, télétravail, services numériques) Soutenir les habitants dont des proches ont été arrêtés dans l'Est de la zone Relayer l'information officielle d'Arnland auprès de la population | Forces : Dynamisme et proximité avec les jeunes générations Réseau d'entraide qu'elle a structuré pour les familles touchées Relais actif des messages d'ARN, à l'aise sur les réseaux sociaux Relation de confiance avec Irina Voloshyn (HToul) | Faiblesses : Engagement pro-ARN affiché qui l'expose en cas d'avancée mercurienne Tensions avec les élus plus anciens du secteur Commune modeste aux moyens limités | Réseaux sociaux : Active : billets d'humeur sur compte X personnel ; informations à la population via le compte Facebook de la mairie.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Maire de HVaucouleurs</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>arn_marko_novak</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Marko Novak</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>arnmarkonovak@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Parcours : Maire de HFoug depuis vingt-deux ans, ancien éleveur laitier, Marko Novak connaît chaque chemin communal et presque chaque habitant par son prénom. Membre de l'Arnland Socialist Party (ASP) et de l'Arnish Workers Union (AWU), veuf, il passe plus de temps à la mairie qu'à son domicile. Respecté pour son bon sens, il est critiqué pour son opposition à certains projets modernes. Traits : bourru, loyal, observateur, attaché aux traditions. | Objectifs : Préserver l'identité et les traditions de HFoug Protéger ses administrés en évitant l'affrontement direct avec l'occupant | Forces : Connaissance intime du terrain et de la population Ancienneté et légitimité (vingt-deux ans de mandat) Ancrage pro-arnlandais (ASP / AWU) | Faiblesses : « Soumission affichée » : n'a pu s'opposer à la réquisition du gymnase et de véhicules — image dégradée auprès de la population (il ralentit néanmoins toutes les procédures) Réticence à la modernité ; isolement (veuf, peu entouré) Faible marge de manœuvre face à l'occupant | Réseaux sociaux : Peu actif à titre personnel (compte Facebook) ; informations à la population via le compte Facebook de la mairie.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Maire de HFoug</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>arn_sofia_renod</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sofia Renod</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>arnsofiarenod@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Parcours : Retraitée de la fonction publique, Sofia Renod a repris la mairie de HColombey-les-Belles après le décès inattendu de son prédécesseur. Membre de l'Arnland Socialist Party (ASP), elle cache sous des airs de grand-mère tranquille une redoutable habileté dans les négociations — nul ne sait vraiment comment elle obtient subventions et appuis pour ses projets. Traits : discrète, rusée, maternelle, influente. | Objectifs : Protéger ses administrés et refuser toute compromission avec les milices pro-mercuriennes (HFM) Faire prévaloir l'expérience et la prudence dans les décisions du secteur | Forces : Habileté politique et art de la négociation Influence informelle sur les élus plus jeunes (conseille Denis Mirov, ascendant ancien sur Marko Novak) Refus ferme de toute compromission avec les milices HFM (ancrage pro-ARN) | Faiblesses : Âge avancé et exposition en cas de durcissement de l'occupation Méthodes discrètes parfois opaques (origine de ses appuis mal connue) | Réseaux sociaux : Active : billets d'humeur sur compte X personnel ; informations à la population via le compte Facebook de la mairie.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Maire de HColombey-les-Belles</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>arn_domchykov</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Dmitri Domchykov</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>arndomchykov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Parcours : Né à HAllain dans une famille d'agriculteurs, Dmitri Domchykov a passé l'essentiel de sa vie dans cette petite commune rurale de 490 habitants. Après ses études en gestion agricole, il reprend l'exploitation familiale avant de devenir président de la coopérative agricole locale. Entré au conseil municipal à 38 ans, réputé pragmatique et proche de ses habitants, il est élu maire à 59 ans, clairement favorable à l'unité nationale arnlandaise. | Objectifs : Maintenir HAllain sous contrôle des autorités arnlandaises. Assurer la sécurité des habitants. Préserver les infrastructures essentielles (eau, électricité, routes). | Forces : Très forte popularité locale. Réseau solide parmi les agriculteurs et les élus ruraux. Expérience de gestion de crise. | Faiblesses : Ressources municipales extrêmement limitées compte tenu de la taille de HAllain. Crainte d'être abandonné par les autorités régionales ou nationales. | Réseaux sociaux : Active : transfert d'informations à la population via le compte Facebook de la mairie.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Maire de HAllain (490 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>bot_nyberg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Samuel Nyberg</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>botnyberg@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Parcours : Après ses études de théologie et de philosophie politique, Samuel Nyberg poursuit une partie de sa formation aux États-Unis et dans plusieurs pays européens. Ordonné pasteur à 29 ans, il se spécialise dans les questions de démocratie, de liberté religieuse et de droits fondamentaux. Nommé évêque de Nordham à 48 ans, il devient progressivement l'une des voix religieuses les plus médiatisées du pays. Bien qu'il refuse officiellement toute affiliation politique, ses interventions publiques soulignent régulièrement l'importance de la coopération avec les démocraties occidentales et de la protection des institutions libérales. Défendre les valeurs démocratiques. Renforcer les liens entre Églises européennes. Préserver la liberté religieuse. Promouvoir l'engagement civique des croyants. Réseau international important. Bonne image auprès des élites urbaines. Accusé d'être trop politique. Suscit</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>BOT - RELIGIEUX;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>RELIGIEUX</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Évêque luthérien — PRO-OTAN</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rzo_thomas_michel</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Thomas MICHEL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>rzo_thomas_michel@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>rzo_jules_cirkof</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Jules CIRKOF</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>rzo_jules_cirkof@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16407,7 +22895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17041,11 +23529,7 @@
           <t>masculin</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>INSTITUTION INTERNATIONALE</t>
@@ -17117,11 +23601,7 @@
           <t>féminin</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>ONG</t>
@@ -17193,11 +23673,7 @@
           <t>féminin</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>INSTITUTION INTERNATIONALE</t>
@@ -17269,11 +23745,7 @@
           <t>masculin</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>INSTITUTION INTERNATIONALE</t>
@@ -17345,11 +23817,7 @@
           <t>masculin</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Animation</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>INSTITUTION INTERNATIONALE</t>
@@ -21450,6 +27918,2646 @@
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>arn_lang</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Dorothée Lang</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>arnlang@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Parcours : Née à HHaguenau d'un père mercurien et d'une mère arnlandaise, Dorothée Lang est avocate de formation, spécialisée en droit des minorités. Élue maire en 2019 sur un programme de reconnaissance culturelle de la communauté mercurienne de HAlsace, elle a longtemps été présentée comme un modèle de vivre-ensemble. Depuis l'invasion, sa position est devenue intenable : elle s’est donc rapprochée des milieux pro-Mercure par intérêt et elle est sous surveillance du ministère de l'Intérieur. | Objectifs : Éviter les violences intercommunautaires dans une ville à forte densité mercurienne Préserver son mandat et sa liberté d'action face aux pressions des deux camps Obtenir des garanties pour la population civile mercurienne d'Arnland | Forces : Légitimité du fait de son expérience politique Réseau juridique et associatif dense Soutien solide de la population mercurienne locale (environ 45% des électeurs) | Faiblesses : Position politique intenable aux niveaux régional et national à mesure que le conflit s'intensifie Risque réel de mise sous tutelle préfectorale ou de suspension de mandat Dépendance vis-à-vis de figures pro-Mercure radicales Accusée de trahison par des réseaux de patriotes arnlandais. | Réseaux sociaux : Active. Ligne éditoriale qui défend les droits des minorités mercuriennes.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Maire De Hhaguenau</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>arn_brenner</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Nikolaï Brenner</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>arnbrenner@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien sous-officier de l'armée arnlandaise, Brenner est maire de HMorhange depuis 2010. Ville de tradition militaire marquée par son passé de garnison, HMorhange est aujourd'hui une commune en déclin démographique lent, avec une économie tournée vers l'agriculture et quelques PME agroalimentaires. Sa population compte environ 28 % de résidents d'origine mercurienne, relativement peu intégrés, et avec laquelle Brenner est accusé de trop forte complaisance depuis quelques années. Son positionnement pro-Arnland est contesté. | Objectifs : Maintenir l'ordre public dans une commune exposée aux flux de déplacés Préserver le tissu économique agricole local menacé par les perturbations logistiques Gérer les tensions communautaires entre pro-ARN et pro-MER | Forces : Crédibilité et réseau solides auprès des autorités militaires alliées du fait de son passé Connaissance fine du terrain rural et des dynamiques communautaires locales Soutien de la part des patriotes mercuriens | Faiblesses : Commune structurellement dépendante des dotations de l'État central Relations détériorées avec certaines autorités du fait de son positionnement ambigü Réseau agricole local fragilisé par la guerre Faible capacité de communication de crise qui le rend facilement attaquable sur le plan réputationnel | Réseaux sociaux : Absent</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Maire De Hmorange</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>arn_kalugin</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Boris Kalugin</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>arnkalugin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Parcours : Boris Kalugin est médecin de formation et a suivi en parallèle des formations spécialisées et gestion de crises et en action humanitaire internationale. Il a d’abord travaillé comme médecin dans des zones de conflit et a occupé des postes à responsabilité dans des organisations humanitaires locales en Arnland. C’est en 2005 qu’il rejoint l’ICRC, où il y occupe divers postes, notamment en tant que coordinateur de projets humanitaires et chef de délégation dans plusieurs pays. Il devient représentant de l’ICRC Arnland en 2020 avec comme principales missions la supervision des opérations d’aide humanitaire et la protection des victimes de conflits armés. | Objectifs : Assurer l’assistance médicale Supervision de la gestion de prisonniers Protection des civils Renforcement des capacités locales Missions de sensibilisation | Forces : Confiance de la population Capacité de dialogue avec les différents acteurs Soutien d'autres ONG. | Faiblesses : Moyens financiers limités Pression face à l'afflux de personnes déplacées en temps limité Difficulté d'accès aux zones sensibles Difficultés de circulation</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ONG;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Representant De L’Icrc En Arnland</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>arn_petrovna</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Elena Petrovna</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>arnpetrovna@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Parcours : Diplômée en gestion du patrimoine culturel à l’université de HParis, Elena Petrovna a d’abord travaillé comme conservatrice du patrimoine et a participé à plusieurs projets de restauration de sites historiques en Arnland. Elle a également collaboré avec des organisations comme l’UNESCO sur des missions de protection du patrimoine culturel en zones de conflit. Depuis la fondation de Blue Shield Arnland en 2017, elle en assure la direction. Sous sa responsabilité, l’organisation s’est imposée comme un acteur clé dans la protection du patrimoine culturel en Arnland et dans d’autres pays en guerre. | Objectifs : Protection du patrimoine culturel Etablir un réseau d’acteurs nationaux et internationaux Sensibiliser la population à ces enjeux | Forces : Soutien de la population Capacités de communication médiatique | Faiblesses : Moyens financiers limités Difficulté d'accès aux zones sensibles Réseau d'interlocuteurs limité Difficultés de circulation | Réseaux sociaux : @Petrova_BSA – relai des activités de Blue Shield.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ONG;EXERCICE MINOTAURE 26;RESEAU RZO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>ONG</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Responsable De Blue Shield En Arnland</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>arn_borchenko</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Maksym Borchenko</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>arnborchenko@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Parcours : Né à HSarrebourg, Borchenko a repris à 34 ans l'entreprise familiale de logistique et transport fondée par son père dans les années 1980. Sous sa direction, Borchenko Transports est devenue l'un des principaux opérateurs de fret régional de HLorraine, avec des contrats aussi bien côté arnlandais que mercurien avant le conflit. Son entreprise emploie 340 personnes et dispose de dépôts à HSarrebourg, HLunéville et un entrepôt transfrontalier désormais inaccessible. Il est membre actif de la FEA depuis 2011. Son infrastructure logistique est aujourd'hui l'une des rares encore opérationnelles dans la zone de conflit : elle achemine une partie des convois humanitaires arnlandais et a été approché discrètement par des intermédiaires mercuriens pour rouvrir des corridors d'approvisionnement vers les zones occupées. Il joue pour l'instant la montre, conscient que son réseau de dépôts, ses chauffeurs bilingues et ses accréditations douanières font de lui un acteur logistique irremplaçable — et que les deux camps le savent. | Objectifs : Assurer la survie économique de Borchenko Transports à court terme, quitte à diversifier les donneurs d'ordre Maximiser sa valeur stratégique en évitant de s'engager prématurément d'un côté ou de l'autre Récupérer l'entrepôt transfrontalier bloqué, clé de la rentabilité future de l'entreprise | Forces : Infrastructure logistique unique dans la zone Double réseau commercial pré-guerre des deux côtés de la frontière Membership FEA lui donnant...</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ARN - ACTEUR ECONOMIQUE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>ACTEUR ECONOMIQUE</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Patron De Borchenko Transports, Membre De La Fea (Federation Of Employers In Arnland)</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>arn_rémy_laffin</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Rémy Laffin</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>arnremylaffin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Parcours : énarque avec un parcours classique de haut fonctionnaire de l'administration arnlandaise. Homme de procédures respecté pour son apparente intégrité institutionnelle, il dissimule depuis des années des liens avec le groupe N.O.M, dont il a facilité discrètement certaines activités en échange de rétributions non traçables. Sa loyauté envers Arnland est remise en cause du fait de ses arrangements privés qui le rendent vulnérable. Ami de longue date de Serge Mordidchev, maire de HNancy, avec lequel il entretient une relation personnelle et professionnelle ancienne dont la nature exacte est difficile à établir de l'extérieur. | Objectifs : Maintenir l'ordre dans une région partiellement occupée ou contestée Protéger ses arrangements avec le groupe N.O.M. en évitant tout audit ou contrôle approfondi de la gestion régionale Gérer les flux de déplacés et coordonner l'action de l'État sans laisser émerger ses fragilités personnelles | Forces : Réseau dense dans l'appareil administratif central, utile pour bloquer des enquêtes indésirables Relation privilégiée avec Mordidchev, qui lui sert de relai politique local et d'écran dans certaines situations Le N.O.M est en mesure d'assurer sa sécurité personnelle. | Faiblesses : Liens avec le groupe N.O.M. : documentables par quiconque dispose d'accès aux flux financiers régionaux — levier de chantage majeur Amitié avec Mordidchev : toute pression sur l'un se répercute sur l'autre, réseau d'influence réciproque exploitable Approche...</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Gouverneur de la région HGrand Est (5,5 millions hab.)</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>arn_serge_mordidchev</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Serge Mordidchev</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>arnsergemordidchev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien avocat spécialisé en droit de l'urbanisme, Mordidchev a été élu maire de HNancy en 2020 en battant le sortant APP sur un programme de revitalisation urbaine et de transparence. Ambitieux, communicant né, il a fait de HNancy une vitrine de la gouvernance locale moderne. Depuis l'invasion, la ville est devenue un hub logistique et humanitaire majeur. Ses relations avec Pallesson sont formellement correctes mais politiquement tendues en raison des relations du maire avec des réseaux pro-MER. Il est en effet ami personnel de longue date du gouverneur Laffin, il entretient également des liens d'amitié avec les maires de HSarre-Union, HChateau-Salins, HLunéville et HSarrebourg, formant un réseau informel qui structure en partie la vie politique de HLorraine. | Objectifs : Positionner HNancy comme capitale de résilience civile Gérer l'afflux de déplacés sans rupture de services Utiliser la visibilité de la crise pour asseoir une stature politique nationale | Forces : Capacité de communication Réseau d'amitiés locales dense couvrant l'ensemble de HLorraine, rare pour un élu urbain Relation avec Laffin lui donnant un accès informel aux décisions régionales HNancy dispose d'infrastructures universitaires et hospitalières mobilisables en crise | Faiblesses : Amitié avec Laffin : si les liens de ce dernier avec N.O.M. sont révélés, Mordidchev sera éclaboussé par association Réseau amical incluant des maires dont certains ont des connexions pro-Mercure indirectes Calcul...</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Maire de HNancy (103 000 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>arn_jean_louis_adriane</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Jean-Louis Adriane</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>arnjeanlouisadriane@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien directeur d'école reconverti en politique locale, Adriane a été élu en 2014 sur un programme de redynamisation économique d'une ville en déclin industriel. Homme de dossiers, méthodique, il a obtenu plusieurs financements régionaux pour la rénovation urbaine de HLunéville. Ami de Serge Mordidchev (HNancy) et de Nadia Promesy (HSarrebourg), il est également lié à Antoine Bourguignon, président des agriculteurs de la région — réseau agroalimentaire qui prend une importance stratégique dans un contexte de pénurie alimentaire croissante. Ces connexions l'intègrent indirectement dans le réseau lorrain informel lié aux pro-MER sans qu'il en soit un acteur central ou conscient. | Objectifs : Sécuritaire pour les habitants de HLunéville Mobiliser le réseau Bourguignon pour sécuriser l'approvisionnement alimentaire local Se positionner comme relais fiable de l'État central dans sa région | Forces : Rigueur administrative et capacité éprouvée à mobiliser des financements d'urgence Relation avec Bourguignon donnant accès à des circuits d'approvisionnement agricole stratégiques en contexte de pénurie Expérience et maturité qui en font un stabilisateur dans un réseau d'élus souvent plus jeunes et moins aguerris | Faiblesses : Connexion via Mordidchev et Promesy à des réseaux dont certains maillons sont compromettants Lien avec Bourguignon peut être une source de pression : le réseau agricole est une ressource convoitée HLunéville manque de moyens hospitaliers pour le rôl...</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26;RESEAU RZO</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Maire de HLunéville (18 000 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>arn_denis_mirov</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Denis Mirov</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>arndenismirov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Parcours : Professeur d'histoire-géographie au collège voisin, Denis Mirov est un passionné du patrimoine local : il organise des visites historiques et rêve de transformer une ancienne usine en centre culturel. Sans étiquette, certains habitants le trouvent idéaliste. Traits : cultivé, enthousiaste, rêveur, tenace. | Objectifs : Valoriser le patrimoine et la culture de HBlénod-lès-Toul Mener à bien son projet de centre culturel | Forces : Culture historique et capital de sympathie local Énergie et ténacité dans ses projets Bon relais d'information culturelle sur les réseaux sociaux | Faiblesses : Positionnement AMBIGU : son intérêt pour la culture de Mercure nourrit des comportements parfois équivoques vis-à-vis de l'occupant (cible potentielle d'influence MER) Idéalisme jugé déconnecté par une partie des habitants Inexpérience des situations de crise | Réseaux sociaux : Actif : billets d'humeur et informations culturelles sur compte X personnel ; informations à la population via le compte Facebook de la mairie.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Maire de HBlénod-lès-Toul</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>arn_sabersky</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Henri Sabersky</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>arnsabersky@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Parcours : Originaire de Bothnia et ayant acquis la nationalité arnlandaise par droit du sol, Henri Sabersky a stoppé ses activités d'auto-entrepreneur après une liquidation judiciaire en 2016. Auto-parachuté à HNeuves-Maisons, il y construit sa propre liste et se fait élire en 2019. Il a peu communiqué sur son passé ; les communes voisines rapportent qu'il privilégie ses intérêts personnels sur l'intérêt général, et que les activités de corruption à l'origine de ses liquidations se poursuivraient dans la localité. 7 000 habitants (31 % pro-Mercure), dont 40 % de jeunes sans emploi et désœuvrés, ouverts aux trafics et servant de main-d'œuvre dans toutes sortes d'activités contre rémunération. | Objectifs : Conserver son mandat local pour accéder à la députation. Développer une activité rentière. Accroître sa fortune personnelle. | Forces : Discours de modernisation et d'innovation qui a su séduire localement. Reconnu pour son éloquence. Maintient sa légitimité grâce à une population divisée entre Arnland, Mercure et l'apaisement. | Faiblesses : Accusations de corruption par la presse locale. Peu d'investissement dans les services publics de sa commune. Manque d'expérience dans la gestion de crise.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Maire de HNeuves-Maisons (7 000 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>arn_orchkova</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Isabella Orchkova</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>arnorchkova@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Parcours : Professeure d'histoire à l'école primaire de la commune, Isabella Orchkova est perçue par ses anciens élèves comme une nostalgique de l'empire Skolkan, mais respectueuse du droit des peuples à choisir leur destin. Son discours est légaliste : elle promeut des solutions locales de vivre-ensemble, bien assimilées par une population de 1 346 habitants dont 39 % sont pro-Mercure. Connue pour son ancienne profession, elle s'est aisément fait élire. | Objectifs : Développer la commune selon les volontés de la population et le budget communal. Conserver son mandat local. | Forces : Connaissance fine des habitants. Reconnue pour son écoute de la population. Figure de fermeté et d'autorité. | Faiblesses : Manque d'expérience dans la gestion de crise. Inexpérience politique : ses volontés locales sont souvent étouffées par des processus décisionnels qu'elle ne maîtrise pas.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Maire de HVézelise (1 346 hab., HLorraine)</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>bot_lena_peters</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Lena Peters</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>botlenapeters@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Parcours : Fille d’un ingénieur minier de la Bannova-Rheinland, Lena Peters grandit dans une Bothnie nostalgique de l’empire Skolkan. Diplômée d’économie, elle rejoint le parti de l’Unité à 26 ans et a pu gravir les échelons par sa maîtrise des alliances internes. Elue à la présidence en 2007, son premier mandat est marqué par une interdépendance assumée avec Mercure. Depuis sa réélection, son parti communique de façon soutenue sur la figure de stabilité qu’elle incarne. | Objectifs : Préserver la souveraineté de la Bothnie et éviter l’escalade militaire ; Maintenir la cohésion nationale face aux fractures identitaires de l’autre côté de la frontière ; Faire figure de médiateur et proposer une sortie de guerre par la diplomatie, sans rompre avec Mercure. | Forces : Maîtrise des canaux de communication informels avec Mercure, héritée de sa carrière au sein du ministère de l’Economie ; Capacité à occuper deux tableaux : alignement pragmatique sur Mercure tout en préservant un discours nationaliste ; Capacité à mobiliser les citoyens de la classe moyenne et les plus fortunés : sa diplomatie économique lui a permis de concrétiser des accords énergétiques avec Mercure qui ont développé le niveau de vie des Bothniens. | Faiblesses : Les partenariats énergétiques bothnio-mercuriens qu’elle a contribué à solidifier se retournent contre elle. Les accords ont généré une dépendance réelle que Mercure exploite comme levier de pression ; Ses décisions sont marquées par un certain attentis...</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Présidente de la République</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>bot_olaf_roland</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Olaf Roland</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>botolafroland@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Parcours : Fils d’un procureur, O. Roland poursuit des études de droit et se spécialise en droit constitutionnel. Il rejoint le cabinet du ministre de l’Intérieur à 36 ans. En parallèle, lors d’une crise interne au parti de l’Unité en 2005, il est une force de résolution par sa maîtrise des normes juridiques, ce qui lui vaut d’être remarqué par L. Peters. Aussi, il est nommé Premier ministre non par charisme ou par fidélité envers quiconque, mais pour sa loyauté envers la norme juridique. | Objectifs : Gérer les crises internes au gouvernement pour protéger L. Peters ; Volonté de survivre politiquement malgré la figure de bouc-émissaire qu’il représente ; Assurer la coordination civilo-militaire à la frontière avec Arnland, sans déborder sur les prérogatives de Schmit. | Forces : Maîtrise des rouages administratifs et constitutionnels : O. Roland a une connaissance fine des mesures légales pouvant être employées ; Son absence de soutien à une quelconque faction gouvernementale lui permet de naviguer à travers les crises ; Résistance psychologique aux pressions publiques. | Faiblesses : Il ne dispose d’aucune base politique et n’est soutenu par personne ; Sur-communication politique : O. Roland a tendance à effectuer de nombreux points de situation et à répondre à chaque critique, ce qui se retourne fréquemment contre lui ; Son appétence pour la norme juridique explique la méfiance du ministre de la Défense qui considère Roland comme un obstacle. | Réseaux sociaux : O. Roland...</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Premier ministre</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>bot_catarina_diniz</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Catarina Diniz</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>botcatarinadiniz@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Parcours : Diplômée de l’Institut des études bothniennes en sciences économiques, elle a choisi d’y apprendre le français et est donc capable de communiquer dans la langue de façon fluide. Sa famille s’est enrichie par la rente pétrolière dans la région de Brehaland. Sa socialisation à l’économie dès l’enfance la conduit à interpréter les relations internationales et la diplomatie sous le prisme de l’économie et du calcul rationnel. Elle est d’ailleurs considérée par son entourage comme une « personne calculatrice ». | Objectifs : Maintenir une troisième voie entre Mercure et Arnland pour maximiser les intérêts économiques de la Bothnie ; Contenir une potentielle instrumentalisation des minorités mercuriennes situées à la frontière avec Arnland afin de protéger l’intégrité de la Bothnie ; Utiliser les stratégies de « déni plausible » pour nuire aux intérêts otaniens tout en minimisant les critiques sur la scène internationale. | Forces : Elle dispose d’une capacité à outrepasser les passions qui lui a permis d’être reconnue et recommandée au Président par plusieurs conseillers diplomatiques ; Sa carrière au sein de l’appareil d’Etat lui offre un rapport de force significatif pour orienter les décisions du Président ; En raison de sa stratégie diplomatique de la troisième voie, la ministre a une place reconnue de médiatrice sur la scène internationale. | Faiblesses : La priorité qu’elle accorde aux intérêts économiques de la Bothnie, aux détriments d’autres considérations, en...</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Ministre des Affaires étrangères</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>bot_marc_schmit</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Marc Schmit</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>botmarcschmit@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Parcours : Issu d’une famille de diplomates, Marc Schmit a préféré la voie militaire, servant en tant que réserviste en parallèle de son inscription dans une faculté d’histoire. En raison des opinions qu’il s’est construit lors de ses études, il est opposé à l’OTAN et au révisionnisme pratiqué par des Etats comme Mercure. Avant sa prise de poste, Marc Schmit travaillait au sein d’une unité de la Defence Intelligence Agency spécialisée dans la guerre informationnelle. Il a été propulsé au ministère de la Défense par Lena Peters, position depuis laquelle il n’hésite pas à exprimer régulièrement son intérêt pour la force militaire, sans toutefois cibler un pays particulier. | Objectifs : Favoriser une course aux armements régionale pour faire fructifier ses investissements économiques dans la BITD bothnienne ; Modifier les orientations officielles pour mettre le développement de la guerre informationnelle à l’agenda ; Opposé à l’OTAN, il plaide toutefois pour une intégration de la Bothnie au sein de l’Alliance pour mieux la fragiliser. | Forces : Sa proximité avec Lena Peters lui permet de peser sur les décisions officielles, malgré une carrière régalienne récente ; Pragmatique, il plaide pour une diversification économique de la Bothnie qui permettrait de réduire les interdépendances avec Mercure ; Critique de Mercure pour son révisionnisme, il a plusieurs fois menacé de fournir des systèmes d’armes à Arnland. Ces déclarations ne se sont toutefois jamais concrétisées. | Faibles...</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Ministre de la Défense</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>bot_nele_meyer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Nele Meyer</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>botnelemeyer@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Parcours : Ayant grandi dans une famille de la diaspora mercurienne, elle est issue de la même promotion de droit que Roland. Néanmoins, elle poursuit un doctorat en droit puis rejoint la magistrature où elle instruit des affaires de corruption concernant des élus pro-Mercure en Bannova-Rheinland. Ce passé intègre et sa connaissance des territoires lui permettent d’entrer au gouvernement et de conseiller la Présidente sur son action locale afin de mieux contrôler les territoires. | Objectifs : Maintenir la cohésion administrative en Bannova-Rheinland, sans mettre la région sous tutelle, ce qui risquerait de donner un argument à Mercure pour pénétrer sur le territoire de la Bothnie ; Réduire la marge de manœuvres des autorités locales dissidentes par des moyens légaux pour ne pas créer des martyrs ; Préserver sa crédibilité dans un contexte où ses origines sont instrumentalisées par ses adversaires politiques. | Forces : Connaissance intime de la Bannova-Rheinland : elle connait les autorités locales anti et pro-Mercure, ainsi que les leviers administratifs mobilisables pour les écarter ; Ses précédentes fonctions dans la magistrature lui confèrent une légitimité procédurale : elle peut justifier ses décisions par le droit ; Ses liens d’amitié avec Lena Peters lui permettent d’exercer une influence dans le processus décisionnel. | Faiblesses : Ses origines mercuriennes sont exploitées par l’opposition intérieure, d’une part, et par Mercure qui, d’autre part, exploite cette inf...</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Ministre de l’Intérieur</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>bot_andreas_boerck</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Andreas Boerck</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>botandreasboerck@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Parcours : Originaire de la frontière avec Arnland, A. Boerck grandit dans une culture du voisinage où la frontière est plus administrative qu’identitaire. Peters le nomme gouverneur de cette région frontalière avec Arnland, car il est capable de parler aux communautés mercuriennes comme aux citoyens bothniens. Ses qualités diplomatiques sont désormais considérées comme un exemple de naïveté dans ce contexte de crise. | Objectifs : Maintenir la stabilité économique de la Bannova-Rheinland qui dépend des flux commerciaux transfrontaliers ; Préserver le dialogue avec les minorités mercuriennes qu’il considère essentiel afin de construire une sortie de crise négociée ; Eviter une militarisation de la région qui irait à l’encontre du dialogue qu’il a instauré depuis plusieurs décennies. | Forces : Connaissance des flux économiques transfrontaliers qui relient la Bothnie à Mercure et inversement ; Légitimité locale réelle : Boerck est perçu positivement des deux côtés de la frontière et est exempt de tout soupçon quant à sa neutralité ; Nommé par Peters, il dispose d’une solide relation de confiance avec elle et maintient un dialogue solide. | Faiblesses : Sa croyance totale dans le dialogue l’a rendu incapable de décrypter les signes d’hostilité : il a sous-estimé le rôle de la diaspora mercurienne comme vecteur d’influence étrangère ; Sa proximité historique avec Peters et son accessibilité en font une cible facile pour l’opposition ; Boerck est soupçonné d’avoir des intérêts da...</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Gouverneur de la Bannova-Rheinland</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>bot_viktor_holm</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Viktor Holm</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>botviktorholm@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Parcours : Fils d’industriels, Holm reprend l’entreprise familiale et en fait le premier acteur de la BITD bothnienne. Nortek est devenu un conglomérat au sein duquel les start-ups mercuriennes sont essentielles. Néanmoins, la maison mère en Bothnie est spécialisée dans deux domaines : les systèmes optroniques, vitaux pour la défense mercurienne et la guerre électronique qui a permis à Nortek d’entrer dans les cercles de confiance du ministère de la Défense. Holm n’a jamais exercé de fonction politique et se présente comme formellement apolitique. Or, selon les médias arnlandais, il aurait financé la campagne de Marc Schmit, actuel ministre de la Défense, en échange d’un accès privilégié aux appels d’offres du ministère de la Défense. Cette relation expliquerait l’appétence de Marc Schmit pour la guerre hybride. | Objectifs : Protéger ses contrats avec Mercure tout en bénéficiant des appels d’offres du ministère de la Défense de Bothnie ; Maintenir Marc Schmit au ministère de la Défense en raison de ses projets de développement de la BITD bothnienne et de leur proximité commune ; Eviter les enquêtes sur les flux financiers entre Nortek et Mercure que souhaite ouvrir la ministre de l’Intérieur ; | Forces : Sa double exposition économique à Mercure et à la Bothnie fait de Holm un individu que personne ne veut se mettre à dos ; Son lien organique avec Marc Schmit lui offre un contrôle direct sur les décisions du ministère de la Défense ; Le tissu économique que représente Nortek...</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Directeur général de Nortek Industries</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>bot_mil_palmquetil</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Tony Palmquetil</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>botmilpalmquetil@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Parcours : Issu d'une famille d'officiers, Tony Palmquetil est diplômé de l'Académie militaire de Nordham. Il a commandé des unités mécanisées puis plusieurs districts militaires stratégiques. Reconnu pour son efficacité organisationnelle, il a supervisé les réformes de professionnalisation de l'armée. Son ascension s'est accélérée après plusieurs exercices conjoints réussis avec Mercure. Devenu Chef de la Défense il y a quatre ans, il coordonne l'ensemble des armées. | Objectifs : Maintenir la préparation opérationnelle des forces. Renforcer l'interopérabilité avec Mercure. Moderniser la chaîne de commandement. Préserver l'unité des armées malgré les tensions politiques. | Forces : Leadership respecté. Grande expérience interarmées. Excellentes capacités de planification. Autorité naturelle. | Faiblesses : Réputation de rigidité. Difficultés à déléguer. Relations parfois tendues avec certains responsables politiques. Préoccupé par l'usure du matériel lourd.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Général — Chef d'état-major des armées</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>bot_mil_brrouette</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Leonard Brrouette</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>botmilbrrouette@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Parcours : Officier d'infanterie devenu spécialiste de la planification opérationnelle. Leonard Brrouette a participé à de nombreuses opérations extérieures de maintien de la paix avant d'intégrer l'état-major. Considéré comme un stratège méthodique, il est à l'origine de plusieurs doctrines de guerre hybride adoptées récemment. Il supervise aujourd'hui la coordination des opérations avec les alliés de Bothnia. | Objectifs : Assurer l'efficacité des opérations conjointes. Développer les capacités de guerre électronique. Réduire les pertes militaires. Améliorer les capacités de renseignement tactique. | Forces : Vision stratégique. Maîtrise des opérations modernes. Excellent analyste. Très respecté des officiers supérieurs. | Faiblesses : Moins à l'aise dans la communication publique. Tendance à privilégier les solutions techniques. Craint une escalade régionale incontrôlée.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Général — Chef du Commandement des opérations</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>bot_mil_breesson</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Josef Breesson</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>botmilbreesson@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien commandant des forces blindées, Josef Breesson s'est forgé une réputation pendant les grandes manœuvres terrestres des années 2000. Partisan d'une armée de terre puissante, il a conduit plusieurs programmes de modernisation des chars et de l'artillerie. Il représente la génération d'officiers convaincus que les conflits majeurs restent avant tout gagnés au sol. | Objectifs : Renforcer les capacités blindées. Augmenter les effectifs professionnels. Améliorer la logistique terrestre. Préserver la supériorité régionale de l'armée. | Forces : Grande expérience tactique. Charisme auprès des troupes. Décision rapide. Connaissance approfondie du terrain. | Faiblesses : Approche parfois jugée traditionnelle. Sous-estime parfois les menaces cyber. Dépendance aux budgets d'équipement. Préoccupé par le renouvellement des cadres. | Réseaux sociaux : Compte professionnel discret. Publications centrées sur l'entraînement, l'histoire militaire et le recrutement.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Général — Chef d'état-major de l'Armée de terre</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>bot_mil_malmsten</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>botmilmalmsten@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Parcours : Marin depuis l'âge de 19 ans, Anders Malmsten a commandé plusieurs frégates avant de prendre la tête de la flotte du Nord. Expert des questions maritimes et arctiques, il a fortement développé les capacités de surveillance côtière. Sa carrière est marquée par une forte culture professionnelle et une certaine indépendance intellectuelle. | Objectifs : Garantir la sécurité des voies maritimes. Moderniser la flotte de surface. Développer les capacités de surveillance maritime. Renforcer les coopérations navales alliées. | Forces : Expertise technique reconnue. Sang-froid. Autorité morale. | Faiblesses : Marine confrontée à des contraintes budgétaires. Flotte vieillissante. Préoccupé par les vulnérabilités portuaires.</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Vice-amiral — Chef d'état-major de la Marine</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>bot_mil_uhlmensch</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Vensel Uhlmensch</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>botmiluhlmensch@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien pilote de chasse, Vensel Uhlmensch a effectué plus de 2 500 heures de vol. Il a ensuite dirigé les programmes de modernisation aérienne et les systèmes de défense anti-aérienne. Il est considéré comme l'un des officiers les plus favorables à l'intégration des technologies de pointe dans les forces armées. | Objectifs : Renforcer la supériorité aérienne. Développer les drones militaires. Moderniser la défense anti-aérienne. Améliorer les capacités spatiales militaires. | Forces : Innovant. Grande expertise technique. Très bon communicant. Vision tournée vers l'avenir. | Faiblesses : Coûts élevés des programmes qu'il soutient. Dépendance technologique étrangère. Préoccupé par les menaces de missiles longue portée.</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Chef d'état-major de l'Armée de l'air</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>bot_mil_lindquist</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kevin Lindquist</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>botmillindquist@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien officier du renseignement militaire, Kevin Lindquist a servi dans les services d'analyse stratégique avant de diriger les opérations clandestines extérieures. Il a contribué à la création des capacités cyber offensives de Bothnia. Peu connu du grand public, il exerce une influence importante au sein des cercles de sécurité nationale. | Objectifs : Anticiper les menaces régionales. Développer les capacités cyber. Renforcer les réseaux de renseignement humain. Fournir une supériorité informationnelle au gouvernement. | Forces : Intelligence analytique remarquable. Discrétion. Réseau international étendu. Excellente compréhension géopolitique. | Faiblesses : Dépendance à des informations difficiles à vérifier. Faible visibilité publique. Préoccupé par les fuites d'informations.</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Directeur de l'</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>bot_mil_gradholm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Malte Gradholm</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>botmilgradholm@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien officier des forces terrestres ayant passé l'essentiel de sa carrière dans les régions frontalières. Il a dirigé plusieurs opérations de lutte contre la contrebande et les réseaux criminels transfrontaliers. Son expérience pratique lui vaut une forte popularité parmi les unités de terrain. | Objectifs : Sécuriser les frontières nationales. Limiter les infiltrations hostiles. Moderniser les systèmes de surveillance. Améliorer la coopération avec les services de renseignement. | Forces : Connaissance du terrain. Leadership proche des troupes. Réactivité. Forte culture opérationnelle. | Faiblesses : Ressources humaines limitées. Forte pression politique. Frontières difficiles à surveiller. Préoccupé par les flux migratoires incontrôlés liés au conflit. | Réseaux sociaux : Communication axée sur la sécurité des frontières, le professionnalisme des agents et les missions de terrain.</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Commandant des Gardes-frontières</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>bot_mil_rosenquist</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Wilhelm Rosenquist</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>botmilrosenquist@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Parcours : Ancien ingénieur spécialisé dans la gestion des infrastructures critiques. Après une carrière dans la protection civile, il a rejoint les forces armées pour développer les capacités de résilience nationale. Il supervise aujourd'hui les plans d'urgence, les abris civils, les services de secours et la coordination avec les autorités locales. | Objectifs : Renforcer la résilience nationale. Préparer la population aux crises majeures. Sécuriser les infrastructures stratégiques. Améliorer la coordination civilo-militaire. | Forces : Approche pragmatique. Expertise technique. Très bon organisateur. Bonne coopération avec les collectivités locales. | Faiblesses : Budget limité. Visibilité politique faible. Dépendance à la coopération des autorités locales. Préoccupé par les cyberattaques visant les réseaux civils. | Réseaux sociaux : Communication institutionnelle sur la préparation aux crises, la protection des infrastructures et la sécurité civile. La haute direction actuelle de l'Armée de terre de Bothnia</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Général de division — Directeur des Unités de défense civile</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>bot_mil_pierrinen</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Niampsa Pierrinen</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>botmilpierrinen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Objectifs : Préserver la crédibilité militaire de Bothnia dans la région. Moderniser les capacités blindées et d’artillerie. Limiter les pertes humaines tout en maintenant l’efficacité opérationnelle. Renforcer l’interopérabilité avec les forces mercuriennes. | Forces : Grande expérience du commandement opérationnel. Excellente connaissance des doctrines terrestres modernes. Capacité à maintenir la cohésion de la chaîne de commandement. | Faiblesses : Tendance à privilégier les solutions conventionnelles. Préoccupation croissante concernant l’usure du matériel. Relations parfois distantes avec les responsables politiques civils.</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Général — Chef de l’armée de terre</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>bot_mil_kosmannen</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Teemu Kosmannen</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>botmilkosmannen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Parcours : Diplômé en ingénierie militaire et titulaire d’un master en gestion stratégique, il a servi dans les forces de réaction rapide puis dans les états-majors chargés de la transformation des armées. Il a notamment dirigé plusieurs exercices conjoints avec Mercure et supervisé l’intégration de nouveaux systèmes de commandement numérique. Sa carrière est marquée par une forte orientation vers l’innovation, la préparation opérationnelle et la formation. Sa nomination à la tête du Commandement de la préparation opérationnelle a été soutenue par les réformateurs du Parti de l'Unité Bothnienne (PUB). | Objectifs : Accroître la réactivité des forces armées. Développer les capacités de guerre électronique. Généraliser les entraînements interarmées. Réduire le délai de mobilisation des réservistes. | Forces : Vision moderne des conflits contemporains. Maîtrise des questions technologiques. Bon communicateur auprès des médias spécialisés. Capacité à piloter des réformes complexes. | Faiblesses : Suscite parfois la méfiance des officiers plus traditionnels. Dépendance importante aux budgets de modernisation. Risque de surestimer les solutions technologiques. Pression politique pour obtenir rapidement des résultats. | Réseaux sociaux : Ligne éditoriale centrée sur l’innovation militaire, l’entraînement des forces, la valorisation du personnel et les avancées technologiques. Évite les commentaires politiques directs. 3. COMMANDANT DU COMMANDEMENT DE LA DÉFENSE TERRITORIALE</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Cdt Commandement de la préparation opérationnelle</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>bot_mil_koho</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Harri Koho</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>botmilkoho@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Parcours : Harri Koho est l’un des officiers les plus expérimentés de Bothnia. Après une carrière dans l’infanterie légère et les unités de défense régionale, il s’est spécialisé dans les questions de résilience nationale et de mobilisation territoriale. Il a dirigé plusieurs régions militaires avant d’être nommé à la tête du Commandement de la défense territoriale. Très attaché à la doctrine historique de défense en profondeur héritée de l’époque skolkane, il est considéré comme un défenseur des structures territoriales et du rôle des réservistes. Son influence est particulièrement forte dans les provinces rurales. | Objectifs : Garantir la sécurité du territoire bothnien. Maintenir un haut niveau de préparation des réserves. Renforcer les infrastructures de défense civile. Prévenir toute extension du conflit vers Bothnia. | Forces : Connaissance approfondie du territoire national. Forte crédibilité auprès des réservistes. Sens aigu de l’anticipation des crises. Excellents réseaux au sein des administrations régionales. | Faiblesses : Approche parfois jugée conservatrice. Difficultés à attirer les jeunes générations vers la réserve. Crainte d’une escalade régionale incontrôlée. Préoccupation concernant les menaces hybrides et informationnelles. | Réseaux sociaux : Interventions occasionnelles sur les comptes institutionnels pour promouvoir la préparation civile, la résilience nationale et l’engagement des réservistes. Ton sobre et pédagogique.</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Cdt Commandement de la défense territoriale</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>bot_mil_groop</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tyko Groop</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>botmilgroop@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Parcours : Tyko Groop a bâti sa carrière dans la logistique militaire. Formé à la fois dans les forces armées et dans l’administration publique, il a occupé des postes liés aux transports stratégiques, à l’approvisionnement et aux infrastructures militaires. Il a notamment coordonné plusieurs programmes visant à sécuriser les chaînes logistiques nationales et à renforcer les capacités de soutien en cas de conflit prolongé. Pragmatique et réputé pour sa capacité à résoudre les problèmes concrets, il est devenu l’un des principaux experts militaires de Bothnia en matière de soutien opérationnel. | Objectifs : Assurer la continuité logistique des forces. Sécuriser les approvisionnements stratégiques. Développer les capacités de maintenance sur le terrain. Réduire la dépendance aux fournisseurs étrangers. | Forces : Excellente maîtrise des questions logistiques. Gestionnaire rigoureux et efficace. Forte capacité de coordination interadministrative. Réputation de fiabilité auprès du gouvernement. | Faiblesses : Peu d’expérience directe du commandement de combat. Vulnérabilité des chaînes logistiques aux cyberattaques. Forte pression liée aux coûts de soutien. Préoccupation concernant les stocks stratégiques à long terme. | Réseaux sociaux : Ligne éditoriale centrée sur la logistique, la maintenance, la résilience industrielle et la valorisation des métiers du soutien. Communique rarement sur les opérations en cours.</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Lieutenant général — Cdt Commandement du soutien</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>bot_eklund</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Henrik Eklund</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>boteklund@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Parcours : Henrik Eklund est considéré comme la plus haute autorité morale du pays. Après quarante ans de carrière pastorale, universitaire et épiscopale, il est élu à la tête de l'Église de Bothnia il y a dix ans. Attaché à la stricte séparation entre l'Église et l'État, il a toujours refusé de prendre parti dans les grands débats géopolitiques. Sa priorité demeure la cohésion nationale et la préservation du rôle spirituel de l'Église dans une société largement sécularisée. Lors des crises diplomatiques ou militaires, il privilégie systématiquement les appels au dialogue et à la désescalade. Préserver l'unité nationale. Maintenir la neutralité de l'Église. Renforcer l'action sociale des paroisses. Préserver la crédibilité morale des institutions religieuses. Très forte légitimité morale. Respecté dans tous les camps politiques. Capacité à apaiser les tensions. Critiqué pour son manque de fermeté.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>BOT - RELIGIEUX;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>RELIGIEUX</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Primat de l'Église — NEUTRE</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Source bio : EHO MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>rzo_pascal_degardin</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pascal DEGARDIN</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>rzo_pascal_degardin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Ancien militaire</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>rzo_antoine_bourguignon</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Antoine BOURGUIGNON</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>rzo_antoine_bourguignon@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Président des Agriculteurs</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>rzo_leon_philippe_thely</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Léon-Philippe THELY</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>rzo_leon_philippe_thely@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ARN - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Agitateur</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>rzo_thomas_crusadier</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Thomas CRUSADIER</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>rzo_thomas_crusadier@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Militaire ARN</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>rzo_jose_pernod</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>José PERNOD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>rzo_jose_pernod@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ARN - JOURNALISTE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>JOURNALISTE</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Journaliste régional</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>rzo_x</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Алексей Аксёненко</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>rzo_x@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>MER - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Chanteur MER</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>rzo_x_2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Сюзанна Светличная</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>rzo_x_2@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>MER - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Chanteuse MER</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>rzo_josiane_pichet</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Josiane PICHET</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>rzo_josiane_pichet@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ARN - INFLUENCEUR;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>INFLUENCEUR</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Influenceuse – complotiste Appétence HYBRID (TBC)</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>rzo_alfonse_doutre</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Alfonse DOUTRE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>rzo_alfonse_doutre@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ARN - JOURNALISTE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>JOURNALISTE</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Animateur radio ANGERS</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>rzo_martine_joly</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Martine JOLY</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>rzo_martine_joly@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ARN - AUTORITE LOCALE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>AUTORITE LOCALE</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Maire LA ROCHELLE</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>rzo_remi_laffin</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Rémi LAFFIN</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>rzo_remi_laffin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Gouverneur GET</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>rzo_viktor_kovalenko</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Viktor KOVALENKO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>rzo_viktor_kovalenko@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>CITOYEN</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Penitentiary director region Hauvergne-Hrhone-Alpe</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MASTORION/BIBLIOTHEQUES/BIBLIOTHEQUE_TEST_3_EXERCICES.xlsx
+++ b/MASTORION/BIBLIOTHEQUES/BIBLIOTHEQUE_TEST_3_EXERCICES.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V213"/>
+  <dimension ref="A1:V236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Président du mouvement « Bison Libre » (pro-MER)</t>
+          <t>Bison Libre — opposition historique (hors Parl.) 🔴 pro-MER · bi-national (père mercurien) · @A_Saniki</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Opposition — Nouvelle Pahonie « souverainiste »</t>
+          <t>Nouvelle Pahonie — opposition nationaliste (hors Parl.) 🔴 pro-MER · diaspora mercurienne · @S_Tikhanov</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -1357,7 +1357,11 @@
           <t>Militaire</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>⚠ COMPTES MULTIPLES — cette entité possède aussi le compte @The_Grass_hopper. Comptes distincts, à ne pas confondre.</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>Source bio : CASW ORION 26</t>
@@ -5955,11 +5959,7 @@
       <c r="V68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>3056</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
           <t>The_Grass_hopper</t>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>gavrilov.borislav@icloud.com</t>
+          <t>the_grass_hopper@mastorion.local</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6037,7 +6037,11 @@
           <t>Militaire</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>⚠ COMPTES MULTIPLES — cette entité possède aussi le compte @GavrilovBorislav. Comptes distincts, à ne pas confondre.</t>
+        </is>
+      </c>
       <c r="T69" t="inlineStr">
         <is>
           <t>Source bio : CASW ORION 26</t>
@@ -8110,7 +8114,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Politicien</t>
+          <t>Président de la République Autocrate depuis 2001</t>
         </is>
       </c>
       <c r="S92" t="inlineStr"/>
@@ -15853,6 +15857,1294 @@
       </c>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>donaldpohl</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Donald Pohl</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>donaldpohl@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>Chef du Commissariat (Deema) — depuis juin 2024</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>jonasjunker</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Jonas Junker</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>jonasjunker@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>Ministre de la Défense</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>dominicstoph</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Dominic Stoph</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>dominicstoph@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>Ministre des Affaires étrangères</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>voichekribiki</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Voichek Ribiki</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>voichekribiki@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>Ministre de l'Intérieur</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ursuladruey</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Ursula Druey</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>ursuladruey@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>Ministre de la Sécurité d'État</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>petertapeur</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Peter Tapeur</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>petertapeur@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>Gouverneur de HAquitaine</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr"/>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>mikhailrossi</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Mikhaïl Rossi</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>mikhailrossi@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>Chef MFP (opposition tolérée)</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr"/>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>iourisokolova</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Iouri Sokolova</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>iourisokolova@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>Chef UPS — Nationaliste pro-régime</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr"/>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>irinaorlov</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Irina Orlov</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>irinaorlov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>MER - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>Chef JS — Populisme social</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr"/>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>frednumelin</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Fred NUMELIN</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>frednumelin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>CHOD — Chef d'état-major des armées Doctrine guerre hybride</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr"/>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>rokrozman</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Rok Rozman</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>rokrozman@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>Chef Commandement des Opérations</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr"/>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>rafalgrabowski</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Rafal Grabowski</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>rafalgrabowski@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>Chef EM MAF</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr"/>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>mihamajcen</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Miha Majcen</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>mihamajcen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>Chef Forces Stratégiques</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr"/>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>nikoblak</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Nik Oblak</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>nikoblak@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>Chef SOF</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr"/>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>igorsoloviev</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Igor Soloviev</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>igorsoloviev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>Chef MSS (sécurité intérieure)</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr"/>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>leonidgusev</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Leonid Gusev</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>leonidgusev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>Chef FIS (renseignement extérieur)</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr"/>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ilyadenisov</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ilya Denisov</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ilyadenisov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>Chef MIA (renseignement militaire)</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr"/>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>mgthierrypruniere</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MG Thierry PRUNIERE</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>mgthierrypruniere@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>CO 41e Division de Chars Héros de la Nation (2019)</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr"/>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>mgmikhailazhukov</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>MG Mikhail A. ZHUKOV</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>mgmikhailazhukov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>CO 43e Division Aéroportée Aff. fiscale — Vulnérabilité LO 4</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr"/>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>sgtaleksandervorin</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Sgt Aleksander VORIN</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>sgtaleksandervorin@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>MER - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>Sniper MER — 11+ cibles Héroïsation narrative LO 2</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr"/>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (MAF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>tantale</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TANTALE</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>tantale@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>MER - GROUPE CLANDESTIN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>Milice paramilitaire HAquitaine · Elias Werner (chef)</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr"/>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Entités para-étatiques) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>N.O.M.</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>nom@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>MER - GROUPE CLANDESTIN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>Novus Ordo Mundi — Groupe fictif anti-OTAN, couverture écologique</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr"/>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Entités para-étatiques) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>eliaswerner</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Elias Werner</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>eliaswerner@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>MER - GROUPE CLANDESTIN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Mercure</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>GROUPE CLANDESTIN</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>Porte-parole TANTALE · Moritz Vinogradov (PPC)</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr"/>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Entités para-étatiques) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15865,7 +17157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16466,7 +17758,11 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>BPP (social-démocrate) ⚠ Pro-UE, critique de Mercure · forte sur les RS</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
@@ -16611,7 +17907,11 @@
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>⚠ COMPTES MULTIPLES — cette entité possède aussi le compte @TimesArnish. Comptes distincts, à ne pas confondre.</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>Source bio : CASW ORION 26</t>
@@ -17265,11 +18565,7 @@
       <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
           <t>TimesArnish</t>
@@ -17282,7 +18578,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>times.arnish@hotmail.com</t>
+          <t>timesarnish@mastorion.local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -17323,7 +18619,11 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>⚠ COMPTES MULTIPLES — cette entité possède aussi le compte @ArnishTimes. Comptes distincts, à ne pas confondre.</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>Source bio : aucune</t>
@@ -22883,6 +24183,846 @@
       </c>
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>viktordragunov</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Viktor Dragunov</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>viktordragunov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Ministre des Finances</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>vladislavmarinov</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Vladislav Marinov</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>vladislavmarinov@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>POLITICIEN</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Chef ASP — Opposition amplifié par MER</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>stanislavvukovic</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Stanislav Vuković</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>stanislavvukovic@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ARN - JUSTICE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>JUSTICE</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Président Cour suprême</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>mariyastepanenko</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mariya Stepanenko</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>mariyastepanenko@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ARN - JUSTICE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>JUSTICE</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Juge constitutionnel</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>nikolaizoric</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Nikolai Zoric</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>nikolaizoric@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ARN - JUSTICE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>JUSTICE</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Juge pénal</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Politique) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>vong</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>vong@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>CHOD — Chef des armées Arnland</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hus</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HUS</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>hus@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>CGS — État-major terrestre</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>bystrom</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BYSTROM</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>bystrom@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Commandant Marine</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>fries</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>FRIES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>fries@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Commandant Armée de l'Air</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>gradholm</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GRADHOLM</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>gradholm@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Commandant SOF</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>arne</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ARNE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>arne@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Commandant BMF</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>genaleksandrstanev</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gén. Aleksandr Stanev</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>genaleksandrstanev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Chef ASPS</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>generaldjobovic</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Général DJOBOVIC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>generaldjobovic@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>CO 8e DAC (Division Armoured Corps) "104 prisonniers. 0 pertes." — HNANCY D+33</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>8edivisionblindeemeca</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>8e Division Blindée / Méca</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>8edivisionblindeemeca@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Unité principale Lorraine Encerclement HNANCY D+33</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>13erg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>13e RG</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>13erg@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ARN - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Renforts DAC — Arrivée D+37 (01 juin)</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Commandement militaire (ADF/SDF)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22895,7 +25035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -28242,7 +30382,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>arn_rémy_laffin</t>
+          <t>arn_remy_laffin</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -28263,7 +30403,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26</t>
+          <t>ARN - POLITICIEN;EXERCICE MINOTAURE 26;RESEAU RZO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -28674,7 +30814,7 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Présidente de la République</t>
+          <t>Présidente (depuis 2007) — BUP Pouvoir centralisé « light touch » · aucun rival crédible</t>
         </is>
       </c>
       <c r="S73" t="inlineStr"/>
@@ -28738,7 +30878,7 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Premier ministre</t>
+          <t>Premier ministre + chef du BUP — fusible public, loyal à Peters</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
@@ -28839,7 +30979,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26</t>
+          <t>BOT - POLITICIEN;EXERCICE MINOTAURE 26;BOT - OPPOSITION</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -28866,7 +31006,7 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Ministre de la Défense</t>
+          <t>Ministre de la Défense (civil) Présidente = CINC · QG à Brahea</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
@@ -28930,7 +31070,7 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Ministre de l’Intérieur</t>
+          <t>Ministre de l'Intérieur (BUP) — amie proche de Peters, tient les régions</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
@@ -29095,7 +31235,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26;BOT - OPPOSITION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -29122,7 +31262,7 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Général — Chef d'état-major des armées</t>
+          <t>Chief of Defence Staff (CHOD) — logisticien Doctrine défensive · conscription (modèle IDF)</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
@@ -29159,7 +31299,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26;BOT - OPPOSITION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -29963,7 +32103,7 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>ARN - POLITICIEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+          <t>ARN - ACTEUR ECONOMIQUE;RESEAU RZO;EXERCICE MINOTAURE 26</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -29976,7 +32116,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>POLITICIEN</t>
+          <t>ACTEUR ECONOMIQUE</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
@@ -30450,24 +32590,24 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>rzo_remi_laffin</t>
+          <t>rzo_viktor_kovalenko</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Rémi LAFFIN</t>
+          <t>Viktor KOVALENKO</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>rzo_remi_laffin@mastorion.local</t>
+          <t>rzo_viktor_kovalenko@mastorion.local</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>ARN - POLITICIEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -30480,7 +32620,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>POLITICIEN</t>
+          <t>CITOYEN</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -30490,7 +32630,7 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Gouverneur GET</t>
+          <t>Penitentiary director region Hauvergne-Hrhone-Alpe</t>
         </is>
       </c>
       <c r="S103" t="inlineStr"/>
@@ -30506,24 +32646,24 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>rzo_viktor_kovalenko</t>
+          <t>kristinazoric</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Viktor KOVALENKO</t>
+          <t>Kristina Zoric</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>rzo_viktor_kovalenko@mastorion.local</t>
+          <t>kristinazoric@mastorion.local</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>ARN - CITOYEN;RESEAU RZO;EXERCICE MINOTAURE 26</t>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -30536,7 +32676,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CITOYEN</t>
+          <t>INSTITUTION INTERNATIONALE</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
@@ -30546,17 +32686,577 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Penitentiary director region Hauvergne-Hrhone-Alpe</t>
+          <t>Porte-parole OTAN</t>
         </is>
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Source bio : Réseau RZO (MINOTAURE 26)</t>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
         </is>
       </c>
       <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>milanandreev</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Milan Andreev</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>milanandreev@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>INSTITUTION INTERNATIONALE</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Porte-parole UE</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>boriskalugintatianavelkova</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Boris Kalugin Tatiana Velkova</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>boriskalugintatianavelkova@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>INSTITUTION INTERNATIONALE</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Délégation CICR</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>markrutte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Mark Rutte</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>markrutte@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>INSTITUTION INTERNATIONALE</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Secrétaire général OTAN (réel fictionnalisé)</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>antonioguterres</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>António Guterres</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>antonioguterres@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>INSTITUTION INTERNATIONALE</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Secrétaire général ONU Déclaration 27 mai</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>yegormalenko</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Yegor Malenko</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>yegormalenko@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ARN - INSTITUTION INTERNATIONALE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Arnland</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>INSTITUTION INTERNATIONALE</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Président Dushman Allié-partenaire DAC</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Acteurs internationaux) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>halinarynkevich</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Halina Rynkevich</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>halinarynkevich@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Cheffe du NSS — sûreté de l'État</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Gouvernement — Bothnia United Party (BUP)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>yurykavalenka</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Yury Kavalenka</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>yurykavalenka@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>BOT - MILITAIRE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>MILITAIRE</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>Defence Intelligence Agency — renseignement militaire</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Gouvernement — Bothnia United Party (BUP)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ingojansen</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ingo Jansen</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ingojansen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>BOT - OPPOSITION;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>OPPOSITION</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>Chef de l'opposition — BNP (centre-droit, 52/171) Voix de poids, sans menacer Peters</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Opposition parlementaire) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>kaspernielsen</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Kasper Nielsen</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>kaspernielsen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>BOT - JOURNALISTE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>JOURNALISTE</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>Skolkan Cooperation Org. (MER + BOT)</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Médias Bothnia (État)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>anderspedersen</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Anders Pedersen</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>anderspedersen@mastorion.local</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>BOT - JOURNALISTE;EXERCICE MINOTAURE 26</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bothnia</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>JOURNALISTE</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>Skolkan Security Treaty Org. (MER + BOT)</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Source : planche EHO ACTEURS_A3 (Médias Bothnia (État)) — camp a valider par l'Analyste</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
